--- a/data/trans_dic/IP1001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen asma</t>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,81</t>
+          <t>0,42; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,47</t>
+          <t>0,44; 4,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,31</t>
+          <t>0,67; 5,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,38</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,83</t>
+          <t>0,97; 4,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,67</t>
+          <t>0,48; 2,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,08</t>
+          <t>0,22; 2,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,39</t>
+          <t>0,25; 2,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,97</t>
+          <t>0,76; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,08</t>
+          <t>0,83; 3,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,34</t>
+          <t>0,74; 4,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,9</t>
+          <t>0,5; 2,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,69</t>
+          <t>1,31; 4,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,09</t>
+          <t>1,13; 3,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,83</t>
+          <t>0,65; 4,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,1</t>
+          <t>0,55; 2,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,58</t>
+          <t>1,29; 3,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,33</t>
+          <t>1,25; 3,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,72</t>
+          <t>0,96; 3,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,63</t>
+          <t>2,06; 7,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,22</t>
+          <t>0,42; 4,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,18</t>
+          <t>2,58; 7,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,63</t>
+          <t>1,29; 5,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,08</t>
+          <t>2,07; 7,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,54</t>
+          <t>0,8; 5,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,05</t>
+          <t>1,53; 6,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 11,34</t>
+          <t>1,91; 10,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,47</t>
+          <t>2,61; 6,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,97</t>
+          <t>0,91; 3,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,02</t>
+          <t>2,65; 6,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,35</t>
+          <t>1,99; 7,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,62</t>
+          <t>3,07; 8,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,22</t>
+          <t>1,07; 5,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,33</t>
+          <t>0,35; 3,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,49</t>
+          <t>0,93; 4,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,68</t>
+          <t>1,59; 5,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,09</t>
+          <t>2,03; 7,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,8</t>
+          <t>1,65; 6,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,18</t>
+          <t>2,44; 7,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,21</t>
+          <t>2,98; 6,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,37</t>
+          <t>2,09; 5,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,94</t>
+          <t>1,21; 3,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,87</t>
+          <t>2,18; 5,25</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,27</t>
+          <t>2,04; 4,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,88</t>
+          <t>1,2; 2,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,3</t>
+          <t>1,48; 3,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,39</t>
+          <t>1,31; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,78</t>
+          <t>1,83; 3,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,86</t>
+          <t>1,87; 3,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,74</t>
+          <t>1,71; 3,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,44</t>
+          <t>2,26; 5,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,63</t>
+          <t>2,18; 3,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,09</t>
+          <t>1,7; 3,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,2</t>
+          <t>1,8; 3,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,91</t>
+          <t>2,12; 3,97</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5085</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3884</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>448; 6491</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>650; 6088</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3052</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>814; 7000</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4471</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3927</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3592</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2198; 10509</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1394; 8210</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>554; 5307</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3597</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2587</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5661</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11528</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9963</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6779</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>641; 6044</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1784; 9623</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1742; 8078</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1173; 7651</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1265; 7255</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3508; 13162</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2911; 10250</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1195; 8241</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2770; 11442</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6474; 17893</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5872; 15766</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3265; 11790</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2267</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8771</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4751</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6336</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9415</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11667</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15107</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>14166</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2624; 10043</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>654; 6875</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4881; 15093</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2229; 10208</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2924; 10647</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1267; 8676</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2888; 11488</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4052; 21397</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7015; 17578</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2853; 11760</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10016; 23665</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7657; 29343</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10266</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4359</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6215</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6887</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7530</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>13371</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17153</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11889</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8157</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>19586</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5955; 16473</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1829; 9427</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>609; 5361</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2570; 11804</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3278; 11897</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3614; 12951</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2880; 11283</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7443; 21643</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11917; 24713</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7283; 17785</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4218; 13530</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>12661; 30498</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20535</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13448</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15761</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>27160</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>39811</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35014</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>41255</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13883; 28151</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8489; 20761</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10432; 24039</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8708; 21961</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13233; 27208</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>14034; 28950</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12716; 26725</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17244; 40171</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>30612; 50416</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>24805; 44239</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>26154; 46007</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>30329; 56621</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Edad-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,11</t>
+          <t>0,43; 5,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,16</t>
+          <t>0,47; 4,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,77</t>
+          <t>0,68; 6,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,62</t>
+          <t>0,87; 4,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,82</t>
+          <t>0,46; 2,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,07</t>
+          <t>0,22; 1,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,39</t>
+          <t>0,28; 2,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,1</t>
+          <t>0,66; 3,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,84</t>
+          <t>0,85; 3,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,8</t>
+          <t>0,72; 4,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,86</t>
+          <t>0,48; 2,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,92</t>
+          <t>1,52; 4,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,97</t>
+          <t>1,14; 4,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,51</t>
+          <t>0,58; 4,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,26</t>
+          <t>0,62; 2,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,56</t>
+          <t>1,34; 3,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,36</t>
+          <t>1,3; 3,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,45</t>
+          <t>0,97; 3,85</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,87</t>
+          <t>2,1; 7,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,44</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,99</t>
+          <t>2,45; 7,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,9</t>
+          <t>0,93; 5,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,52</t>
+          <t>2,18; 7,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,47</t>
+          <t>0,81; 5,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,09</t>
+          <t>1,59; 5,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,07</t>
+          <t>1,9; 10,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,53</t>
+          <t>2,76; 6,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,75</t>
+          <t>0,84; 3,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,27</t>
+          <t>2,6; 5,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,61</t>
+          <t>2,04; 6,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 8,49</t>
+          <t>3,13; 8,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,5</t>
+          <t>1,11; 5,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,09</t>
+          <t>0,36; 3,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,29</t>
+          <t>1,01; 4,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,77</t>
+          <t>1,82; 5,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,28</t>
+          <t>2,28; 7,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,48</t>
+          <t>1,74; 6,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,08</t>
+          <t>2,55; 6,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,18</t>
+          <t>2,93; 6,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,09</t>
+          <t>1,97; 5,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,9</t>
+          <t>1,27; 4,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,25</t>
+          <t>2,2; 5,03</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,13</t>
+          <t>2,15; 4,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,94</t>
+          <t>1,11; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,41</t>
+          <t>1,49; 3,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,3</t>
+          <t>1,31; 3,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,76</t>
+          <t>1,81; 3,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,87</t>
+          <t>1,79; 3,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,59</t>
+          <t>1,79; 3,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,27</t>
+          <t>2,46; 5,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,59</t>
+          <t>2,19; 3,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,04</t>
+          <t>1,69; 3,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,17</t>
+          <t>1,78; 3,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,97</t>
+          <t>2,16; 4,07</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>448; 6491</t>
+          <t>455; 6317</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>650; 6088</t>
+          <t>687; 6373</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 3574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1665,42 +1665,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>814; 7000</t>
+          <t>825; 7531</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4471</t>
+          <t>0; 3967</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3927</t>
+          <t>0; 3589</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3592</t>
+          <t>0; 3535</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2198; 10509</t>
+          <t>1983; 9531</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1394; 8210</t>
+          <t>1338; 7859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>554; 5307</t>
+          <t>560; 4734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3597</t>
+          <t>0; 3634</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>641; 6044</t>
+          <t>707; 6122</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1784; 9623</t>
+          <t>1559; 9359</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1742; 8078</t>
+          <t>1784; 8143</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1173; 7651</t>
+          <t>1150; 7243</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1265; 7255</t>
+          <t>1214; 6709</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3508; 13162</t>
+          <t>4070; 12892</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2911; 10250</t>
+          <t>2954; 10779</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1195; 8241</t>
+          <t>1062; 8396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2770; 11442</t>
+          <t>3148; 11333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6474; 17893</t>
+          <t>6746; 18791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5872; 15766</t>
+          <t>6094; 16128</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3265; 11790</t>
+          <t>3326; 13145</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2624; 10043</t>
+          <t>2676; 9897</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>654; 6875</t>
+          <t>0; 6291</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4881; 15093</t>
+          <t>4621; 14995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2229; 10208</t>
+          <t>1607; 10037</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2924; 10647</t>
+          <t>3091; 10824</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1267; 8676</t>
+          <t>1281; 8909</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2888; 11488</t>
+          <t>2998; 11260</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4052; 21397</t>
+          <t>4046; 22616</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7015; 17578</t>
+          <t>7423; 17673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2853; 11760</t>
+          <t>2631; 11648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10016; 23665</t>
+          <t>9829; 22582</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7657; 29343</t>
+          <t>7853; 26059</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5955; 16473</t>
+          <t>6078; 16048</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1829; 9427</t>
+          <t>1905; 9562</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>609; 5361</t>
+          <t>619; 5829</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2570; 11804</t>
+          <t>2787; 12690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3278; 11897</t>
+          <t>3744; 12263</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3614; 12951</t>
+          <t>4062; 13392</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2880; 11283</t>
+          <t>3031; 11448</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7443; 21643</t>
+          <t>7799; 21268</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11917; 24713</t>
+          <t>11733; 24821</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7283; 17785</t>
+          <t>6892; 18716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4218; 13530</t>
+          <t>4416; 13910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12661; 30498</t>
+          <t>12757; 29212</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13883; 28151</t>
+          <t>14626; 28995</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8489; 20761</t>
+          <t>7856; 20292</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10432; 24039</t>
+          <t>10516; 23805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8708; 21961</t>
+          <t>8724; 21433</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13233; 27208</t>
+          <t>13052; 27270</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14034; 28950</t>
+          <t>13431; 28854</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12716; 26725</t>
+          <t>13327; 27885</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17244; 40171</t>
+          <t>18728; 41195</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30612; 50416</t>
+          <t>30674; 50444</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24805; 44239</t>
+          <t>24619; 44180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26154; 46007</t>
+          <t>25800; 44912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30329; 56621</t>
+          <t>30855; 58133</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,95</t>
+          <t>0,68; 6,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,36</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 9,55</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,42; 5,81</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,46; 4,47</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,87</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,68; 6,2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,75</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,89</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,75</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,19</t>
+          <t>0,99; 4,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,7</t>
+          <t>0,45; 2,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,85</t>
+          <t>0,22; 2,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,42</t>
+          <t>0,5; 2,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,99</t>
+          <t>1,47; 4,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,87</t>
+          <t>1,0; 4,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,55</t>
+          <t>0,71; 5,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,64</t>
+          <t>0,28; 2,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,82</t>
+          <t>0,76; 3,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,18</t>
+          <t>0,85; 4,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,6</t>
+          <t>0,7; 4,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,24</t>
+          <t>0,57; 2,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,74</t>
+          <t>1,35; 3,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,44</t>
+          <t>1,31; 3,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,85</t>
+          <t>1,03; 4,04</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,76</t>
+          <t>2,13; 8,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,8; 5,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,94</t>
+          <t>1,51; 6,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,8</t>
+          <t>1,7; 6,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,65</t>
+          <t>2,04; 7,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,62</t>
+          <t>0,42; 4,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,97</t>
+          <t>2,51; 8,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 10,64</t>
+          <t>0,99; 5,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,57</t>
+          <t>2,6; 6,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,72</t>
+          <t>0,91; 3,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,98</t>
+          <t>2,55; 6,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,76</t>
+          <t>1,77; 5,12</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,27</t>
+          <t>1,68; 5,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,58</t>
+          <t>2,33; 7,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,36</t>
+          <t>1,67; 6,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,61</t>
+          <t>2,55; 7,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,95</t>
+          <t>3,19; 8,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,53</t>
+          <t>0,93; 5,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,58</t>
+          <t>0,35; 3,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,96</t>
+          <t>1,2; 4,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,2</t>
+          <t>2,9; 6,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,36</t>
+          <t>1,95; 5,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,0</t>
+          <t>1,24; 3,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,03</t>
+          <t>2,26; 5,13</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,26</t>
+          <t>1,86; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,87</t>
+          <t>1,81; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,38</t>
+          <t>1,75; 3,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,22</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,77</t>
+          <t>2,1; 4,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,85</t>
+          <t>1,16; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,74</t>
+          <t>1,42; 3,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,41</t>
+          <t>1,47; 3,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,59</t>
+          <t>2,2; 3,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,03</t>
+          <t>1,69; 3,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,1</t>
+          <t>1,82; 3,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,07</t>
+          <t>2,13; 3,77</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,44 +1577,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2145</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2586</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2940</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5085</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>644</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>455; 6317</t>
+          <t>823; 7661</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>687; 6373</t>
+          <t>0; 3943</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3574</t>
+          <t>0; 3726</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 4828</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>450; 6169</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>679; 6536</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2461</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>825; 7531</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3967</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3589</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3535</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1983; 9531</t>
+          <t>2257; 10992</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1338; 7859</t>
+          <t>1299; 7765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>560; 4734</t>
+          <t>558; 5324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3634</t>
+          <t>0; 3216</t>
         </is>
       </c>
     </row>
@@ -1717,37 +1717,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5661</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3322</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2587</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4237</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4302</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3320</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7291</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5661</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6437</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>707; 6122</t>
+          <t>1267; 7361</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1559; 9359</t>
+          <t>3942; 12551</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1784; 8143</t>
+          <t>2578; 10547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1150; 7243</t>
+          <t>1120; 8123</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1214; 6709</t>
+          <t>704; 6053</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4070; 12892</t>
+          <t>1794; 9320</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2954; 10779</t>
+          <t>1797; 8593</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1062; 8396</t>
+          <t>1018; 6890</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3148; 11333</t>
+          <t>2890; 10648</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6746; 18791</t>
+          <t>6804; 17967</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6094; 16128</t>
+          <t>6129; 15595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3326; 13145</t>
+          <t>3113; 12232</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6336</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5537</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2267</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8771</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4751</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6130</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3894</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6336</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>11675</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2676; 9897</t>
+          <t>3008; 11434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6291</t>
+          <t>1270; 8782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4621; 14995</t>
+          <t>2851; 11410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1607; 10037</t>
+          <t>3399; 13038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3091; 10824</t>
+          <t>2598; 9726</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1281; 8909</t>
+          <t>657; 6531</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2998; 11260</t>
+          <t>4748; 15444</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4046; 22616</t>
+          <t>1733; 10180</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7423; 17673</t>
+          <t>6984; 17408</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2631; 11648</t>
+          <t>2862; 12450</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9829; 22582</t>
+          <t>9623; 22739</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7853; 26059</t>
+          <t>6627; 19189</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6887</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7530</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12908</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10266</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4359</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6215</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6887</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7530</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6073</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>19411</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6078; 16048</t>
+          <t>3462; 11710</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1905; 9562</t>
+          <t>4141; 12626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>619; 5829</t>
+          <t>2912; 11839</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2787; 12690</t>
+          <t>7470; 21113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3744; 12263</t>
+          <t>6184; 16723</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4062; 13392</t>
+          <t>1601; 8942</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3031; 11448</t>
+          <t>612; 5777</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7799; 21268</t>
+          <t>3082; 12606</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11733; 24821</t>
+          <t>11611; 24849</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6892; 18716</t>
+          <t>6822; 18756</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4416; 13910</t>
+          <t>4317; 13670</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12757; 29212</t>
+          <t>12425; 28177</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>20535</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>13448</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>19277</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>38166</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14626; 28995</t>
+          <t>13421; 27329</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7856; 20292</t>
+          <t>13587; 28897</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10516; 23805</t>
+          <t>13025; 27863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8724; 21433</t>
+          <t>16067; 33293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13052; 27270</t>
+          <t>14301; 29054</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13431; 28854</t>
+          <t>8232; 20330</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13327; 27885</t>
+          <t>10036; 23232</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18728; 41195</t>
+          <t>9262; 23575</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30674; 50444</t>
+          <t>30919; 50899</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24619; 44180</t>
+          <t>24595; 44948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25800; 44912</t>
+          <t>26405; 46378</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30855; 58133</t>
+          <t>28380; 50180</t>
         </is>
       </c>
     </row>
